--- a/docs/import-data/khoa-nganh-dao-tao-tu-du-lieu-tot-nghiep/khoa-nganh-dao-tao-K59.xlsx
+++ b/docs/import-data/khoa-nganh-dao-tao-tu-du-lieu-tot-nghiep/khoa-nganh-dao-tao-K59.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="96">
   <si>
     <t>Khoá ngành đào tạo</t>
   </si>
@@ -66,6 +66,12 @@
     <t>Điều khiển tàu biển</t>
   </si>
   <si>
+    <t>ĐTĐ59CL</t>
+  </si>
+  <si>
+    <t>Điện tự động công nghiệp (CLC)</t>
+  </si>
+  <si>
     <t>ĐTĐ59ĐH</t>
   </si>
   <si>
@@ -270,16 +276,10 @@
     <t>Đủ điều kiện import</t>
   </si>
   <si>
-    <t>ĐTĐ59CL</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>Điện tự động công nghiệp (CLC) | Điện tự động công nghiệp (NC)</t>
   </si>
   <si>
-    <t>Mâu thuẫn ngành — cần xác minh, chưa đưa vào import</t>
+    <t>Mâu thuẫn tên ngành — đã đối chiếu: Hậu tố CL của mã lớp → chương trình CLC</t>
   </si>
   <si>
     <t>Kỹ thuật công nghệ hóa học</t>
@@ -300,7 +300,7 @@
     <t>Đây là số tối thiểu đã biết, không phải sĩ số đầu khoá. Cần thay bằng sĩ số đầu khoá chính thức nếu có.</t>
   </si>
   <si>
-    <t>Các dòng có nhiều tên ngành mâu thuẫn không được đưa vào sheet import và nằm trong sheet “Đối chiếu nguồn”.</t>
+    <t>Các mã lớp có tên ngành nguồn mâu thuẫn vẫn được đưa vào import theo quy tắc mã lớp; chi tiết nằm trong sheet “Đối chiếu nguồn”.</t>
   </si>
 </sst>
 </file>
@@ -698,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -802,7 +802,7 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -813,7 +813,7 @@
         <v>20</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -824,7 +824,7 @@
         <v>22</v>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -835,7 +835,7 @@
         <v>24</v>
       </c>
       <c r="C12">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -846,7 +846,7 @@
         <v>26</v>
       </c>
       <c r="C13">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -857,7 +857,7 @@
         <v>28</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -868,7 +868,7 @@
         <v>30</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -879,7 +879,7 @@
         <v>32</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -890,7 +890,7 @@
         <v>34</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -912,7 +912,7 @@
         <v>38</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -923,7 +923,7 @@
         <v>40</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -934,7 +934,7 @@
         <v>42</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -945,7 +945,7 @@
         <v>44</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -956,7 +956,7 @@
         <v>46</v>
       </c>
       <c r="C23">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -967,7 +967,7 @@
         <v>48</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -978,7 +978,7 @@
         <v>50</v>
       </c>
       <c r="C25">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -989,7 +989,7 @@
         <v>52</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1000,7 +1000,7 @@
         <v>54</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1022,7 +1022,7 @@
         <v>58</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1055,7 +1055,7 @@
         <v>64</v>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1066,7 +1066,7 @@
         <v>66</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1077,7 +1077,7 @@
         <v>68</v>
       </c>
       <c r="C34">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1088,7 +1088,7 @@
         <v>70</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1099,7 +1099,7 @@
         <v>72</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1110,7 +1110,7 @@
         <v>74</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1121,6 +1121,17 @@
         <v>76</v>
       </c>
       <c r="C38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39">
         <v>10</v>
       </c>
     </row>
@@ -1146,27 +1157,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1181,12 +1192,12 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -1201,12 +1212,12 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -1221,12 +1232,12 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -1241,12 +1252,12 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -1261,12 +1272,12 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -1281,12 +1292,12 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -1301,18 +1312,18 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1326,153 +1337,153 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D12">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D16">
         <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1481,447 +1492,447 @@
         <v>89</v>
       </c>
       <c r="F17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18">
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D19">
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D20">
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D21">
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D22">
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D24">
         <v>14</v>
       </c>
       <c r="E24" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D26">
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D28">
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F28" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D29">
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D30">
         <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D31">
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F31" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D32">
         <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D33">
         <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D34">
         <v>7</v>
       </c>
       <c r="E34" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D35">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D37">
         <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F37" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D38">
         <v>4</v>
       </c>
       <c r="E38" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F38" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D39">
         <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F39" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/docs/import-data/khoa-nganh-dao-tao-tu-du-lieu-tot-nghiep/khoa-nganh-dao-tao-K59.xlsx
+++ b/docs/import-data/khoa-nganh-dao-tao-tu-du-lieu-tot-nghiep/khoa-nganh-dao-tao-K59.xlsx
@@ -6,14 +6,15 @@
   <sheets>
     <sheet sheetId="1" name="Khoa nganh dao tao" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Đối chiếu nguồn" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Hướng dẫn" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Nguồn chỉ tiêu" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="Hướng dẫn" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="155">
   <si>
     <t>Khoá ngành đào tạo</t>
   </si>
@@ -21,7 +22,7 @@
     <t>Ngành đào tạo</t>
   </si>
   <si>
-    <t>Số lượng sinh viên</t>
+    <t>Số lượng sinh viên đầu vào</t>
   </si>
   <si>
     <t>ATM59ĐH</t>
@@ -270,44 +271,221 @@
     <t>Kết luận</t>
   </si>
   <si>
+    <t>Mã CTĐT tuyển sinh</t>
+  </si>
+  <si>
+    <t>Chỉ tiêu công bố</t>
+  </si>
+  <si>
+    <t>Số đầu vào tạm tính áp dụng</t>
+  </si>
+  <si>
+    <t>Căn cứ áp dụng</t>
+  </si>
+  <si>
     <t>K59</t>
   </si>
   <si>
     <t>Đủ điều kiện import</t>
   </si>
   <si>
+    <t>D124</t>
+  </si>
+  <si>
+    <t>Chỉ tiêu tuyển sinh công bố</t>
+  </si>
+  <si>
+    <t>D111</t>
+  </si>
+  <si>
+    <t>A403</t>
+  </si>
+  <si>
+    <t>D117</t>
+  </si>
+  <si>
+    <t>H114</t>
+  </si>
+  <si>
+    <t>D114</t>
+  </si>
+  <si>
+    <t>D101</t>
+  </si>
+  <si>
     <t>Điện tự động công nghiệp (CLC) | Điện tự động công nghiệp (NC)</t>
   </si>
   <si>
     <t>Mâu thuẫn tên ngành — đã đối chiếu: Hậu tố CL của mã lớp → chương trình CLC</t>
   </si>
   <si>
+    <t>H105</t>
+  </si>
+  <si>
+    <t>D105</t>
+  </si>
+  <si>
+    <t>D103</t>
+  </si>
+  <si>
+    <t>D104</t>
+  </si>
+  <si>
+    <t>A408</t>
+  </si>
+  <si>
+    <t>A409</t>
+  </si>
+  <si>
+    <t>D113</t>
+  </si>
+  <si>
+    <t>D116</t>
+  </si>
+  <si>
     <t>Kỹ thuật công nghệ hóa học</t>
   </si>
   <si>
+    <t>D126</t>
+  </si>
+  <si>
+    <t>D115</t>
+  </si>
+  <si>
+    <t>D123</t>
+  </si>
+  <si>
+    <t>D118</t>
+  </si>
+  <si>
+    <t>H401</t>
+  </si>
+  <si>
+    <t>D401</t>
+  </si>
+  <si>
+    <t>D127</t>
+  </si>
+  <si>
+    <t>H402</t>
+  </si>
+  <si>
+    <t>D402</t>
+  </si>
+  <si>
+    <t>D122</t>
+  </si>
+  <si>
+    <t>D410</t>
+  </si>
+  <si>
+    <t>D120</t>
+  </si>
+  <si>
+    <t>D407</t>
+  </si>
+  <si>
+    <t>D102</t>
+  </si>
+  <si>
+    <t>D106</t>
+  </si>
+  <si>
+    <t>D109</t>
+  </si>
+  <si>
+    <t>D125</t>
+  </si>
+  <si>
+    <t>D403</t>
+  </si>
+  <si>
+    <t>D404</t>
+  </si>
+  <si>
+    <t>D411</t>
+  </si>
+  <si>
+    <t>D121</t>
+  </si>
+  <si>
+    <t>D119</t>
+  </si>
+  <si>
+    <t>D112</t>
+  </si>
+  <si>
+    <t>THÔNG TIN NGUỒN</t>
+  </si>
+  <si>
+    <t>GIÁ TRỊ</t>
+  </si>
+  <si>
+    <t>Khóa</t>
+  </si>
+  <si>
+    <t>Năm tuyển sinh</t>
+  </si>
+  <si>
+    <t>Loại dữ liệu</t>
+  </si>
+  <si>
+    <t>Chỉ tiêu tuyển sinh dùng làm số đầu vào tạm tính; KHÔNG phải số sinh viên thực nhập</t>
+  </si>
+  <si>
+    <t>Loại nguồn</t>
+  </si>
+  <si>
+    <t>official_admission_proposal</t>
+  </si>
+  <si>
+    <t>Nguồn</t>
+  </si>
+  <si>
+    <t>https://tuyensinh.vimaru.edu.vn/sites/tuyensinh.vimaru.edu.vn/files/De%20an%20tuyen%20sinh%202018_0.pdf</t>
+  </si>
+  <si>
+    <t>Nguyên tắc</t>
+  </si>
+  <si>
+    <t>Số áp dụng = max(chỉ tiêu công bố, số sinh viên tốt nghiệp duy nhất đã quan sát) để không tạo tỷ lệ tốt nghiệp vượt 100%</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Thay bằng số thực nhập chính thức khi Nhà trường cung cấp dữ liệu.</t>
+  </si>
+  <si>
     <t>HƯỚNG DẪN</t>
   </si>
   <si>
-    <t>Khi import, chọn đúng K59 ở trường “Import vào khoá học”.</t>
+    <t>Khi import, chọn đúng K59 ở trường “Import vào khóa học”.</t>
+  </si>
+  <si>
+    <t>File này chỉ được chứa mã lớp của K59; hệ thống sẽ từ chối file chứa từ hai khóa trở lên.</t>
   </si>
   <si>
     <t>Sheet “Khoa nganh dao tao” là dữ liệu import; hệ thống chỉ đọc sheet đầu tiên.</t>
   </si>
   <si>
-    <t>Số lượng sinh viên trong file này là số mã sinh viên duy nhất quan sát được trong các file tốt nghiệp nguồn.</t>
-  </si>
-  <si>
-    <t>Đây là số tối thiểu đã biết, không phải sĩ số đầu khoá. Cần thay bằng sĩ số đầu khoá chính thức nếu có.</t>
-  </si>
-  <si>
-    <t>Các mã lớp có tên ngành nguồn mâu thuẫn vẫn được đưa vào import theo quy tắc mã lớp; chi tiết nằm trong sheet “Đối chiếu nguồn”.</t>
+    <t>Cột số lượng sinh viên đầu vào hiện dùng chỉ tiêu tuyển sinh công bố làm dữ liệu tạm tính, không phải số thực nhập.</t>
+  </si>
+  <si>
+    <t>Nếu số tốt nghiệp quan sát được lớn hơn chỉ tiêu, file dùng số tốt nghiệp làm cận dưới để tránh tỷ lệ vượt 100%.</t>
+  </si>
+  <si>
+    <t>Xem nguồn, năm công bố và nguyên tắc áp dụng tại sheet “Nguồn chỉ tiêu”.</t>
+  </si>
+  <si>
+    <t>Cần thay dữ liệu tạm tính bằng số thực nhập khi Nhà trường cung cấp dữ liệu chính thức.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -318,9 +496,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <b/>
     </font>
     <font>
       <b/>
@@ -352,13 +527,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -703,10 +886,10 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -725,7 +908,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -736,7 +919,7 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -747,7 +930,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>15</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -758,7 +941,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -769,7 +952,7 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -780,7 +963,7 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -791,7 +974,7 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -802,7 +985,7 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -813,7 +996,7 @@
         <v>20</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -824,7 +1007,7 @@
         <v>22</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -835,7 +1018,7 @@
         <v>24</v>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -846,7 +1029,7 @@
         <v>26</v>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -857,7 +1040,7 @@
         <v>28</v>
       </c>
       <c r="C14">
-        <v>32</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -868,7 +1051,7 @@
         <v>30</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -879,7 +1062,7 @@
         <v>32</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -890,7 +1073,7 @@
         <v>34</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -901,7 +1084,7 @@
         <v>36</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -912,7 +1095,7 @@
         <v>38</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -923,7 +1106,7 @@
         <v>40</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -934,7 +1117,7 @@
         <v>42</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -945,7 +1128,7 @@
         <v>44</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -956,7 +1139,7 @@
         <v>46</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -967,7 +1150,7 @@
         <v>48</v>
       </c>
       <c r="C24">
-        <v>14</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -978,7 +1161,7 @@
         <v>50</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -989,7 +1172,7 @@
         <v>52</v>
       </c>
       <c r="C26">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1000,7 +1183,7 @@
         <v>54</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1011,7 +1194,7 @@
         <v>56</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1022,7 +1205,7 @@
         <v>58</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1033,7 +1216,7 @@
         <v>60</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1044,7 +1227,7 @@
         <v>62</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1055,7 +1238,7 @@
         <v>64</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1066,7 +1249,7 @@
         <v>66</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1077,7 +1260,7 @@
         <v>68</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1088,7 +1271,7 @@
         <v>70</v>
       </c>
       <c r="C35">
-        <v>12</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1099,7 +1282,7 @@
         <v>72</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1110,7 +1293,7 @@
         <v>74</v>
       </c>
       <c r="C37">
-        <v>8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1121,7 +1304,7 @@
         <v>76</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1132,19 +1315,19 @@
         <v>78</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1153,31 +1336,46 @@
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="70" customWidth="1"/>
     <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="30" customHeight="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1192,12 +1390,24 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2">
+        <v>90</v>
+      </c>
+      <c r="I2">
+        <v>90</v>
+      </c>
+      <c r="J2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -1212,12 +1422,24 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H3">
+        <v>45</v>
+      </c>
+      <c r="I3">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -1232,12 +1454,24 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H4">
+        <v>80</v>
+      </c>
+      <c r="I4">
+        <v>80</v>
+      </c>
+      <c r="J4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -1252,12 +1486,24 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5">
+        <v>60</v>
+      </c>
+      <c r="I5">
+        <v>60</v>
+      </c>
+      <c r="J5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -1272,12 +1518,24 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6">
+        <v>60</v>
+      </c>
+      <c r="I6">
+        <v>60</v>
+      </c>
+      <c r="J6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -1292,12 +1550,24 @@
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -1312,12 +1582,24 @@
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8">
+        <v>180</v>
+      </c>
+      <c r="I8">
+        <v>180</v>
+      </c>
+      <c r="J8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -1329,15 +1611,27 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9">
+        <v>60</v>
+      </c>
+      <c r="I9">
+        <v>60</v>
+      </c>
+      <c r="J9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -1352,12 +1646,24 @@
         <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10">
+        <v>90</v>
+      </c>
+      <c r="I10">
+        <v>90</v>
+      </c>
+      <c r="J10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
@@ -1372,12 +1678,24 @@
         <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11">
+        <v>45</v>
+      </c>
+      <c r="I11">
+        <v>45</v>
+      </c>
+      <c r="J11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
@@ -1392,12 +1710,24 @@
         <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12">
+        <v>90</v>
+      </c>
+      <c r="I12">
+        <v>90</v>
+      </c>
+      <c r="J12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
         <v>25</v>
@@ -1412,12 +1742,24 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13">
+        <v>60</v>
+      </c>
+      <c r="I13">
+        <v>60</v>
+      </c>
+      <c r="J13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -1432,12 +1774,24 @@
         <v>28</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14">
+        <v>80</v>
+      </c>
+      <c r="I14">
+        <v>80</v>
+      </c>
+      <c r="J14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
@@ -1452,12 +1806,24 @@
         <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H15">
+        <v>45</v>
+      </c>
+      <c r="I15">
+        <v>45</v>
+      </c>
+      <c r="J15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -1472,12 +1838,24 @@
         <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H16">
+        <v>90</v>
+      </c>
+      <c r="I16">
+        <v>90</v>
+      </c>
+      <c r="J16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
@@ -1489,15 +1867,27 @@
         <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G17" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17">
+        <v>45</v>
+      </c>
+      <c r="I17">
+        <v>45</v>
+      </c>
+      <c r="J17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
@@ -1512,12 +1902,24 @@
         <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G18" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18">
+        <v>90</v>
+      </c>
+      <c r="I18">
+        <v>90</v>
+      </c>
+      <c r="J18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
@@ -1532,12 +1934,24 @@
         <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G19" t="s">
+        <v>112</v>
+      </c>
+      <c r="H19">
+        <v>45</v>
+      </c>
+      <c r="I19">
+        <v>45</v>
+      </c>
+      <c r="J19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
@@ -1552,12 +1966,24 @@
         <v>40</v>
       </c>
       <c r="F20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G20" t="s">
+        <v>113</v>
+      </c>
+      <c r="H20">
+        <v>45</v>
+      </c>
+      <c r="I20">
+        <v>45</v>
+      </c>
+      <c r="J20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
@@ -1572,12 +1998,24 @@
         <v>42</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G21" t="s">
+        <v>114</v>
+      </c>
+      <c r="H21">
+        <v>90</v>
+      </c>
+      <c r="I21">
+        <v>90</v>
+      </c>
+      <c r="J21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
@@ -1592,12 +2030,24 @@
         <v>44</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G22" t="s">
+        <v>115</v>
+      </c>
+      <c r="H22">
+        <v>135</v>
+      </c>
+      <c r="I22">
+        <v>135</v>
+      </c>
+      <c r="J22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
         <v>45</v>
@@ -1612,12 +2062,24 @@
         <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G23" t="s">
+        <v>116</v>
+      </c>
+      <c r="H23">
+        <v>45</v>
+      </c>
+      <c r="I23">
+        <v>45</v>
+      </c>
+      <c r="J23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
         <v>47</v>
@@ -1632,12 +2094,24 @@
         <v>48</v>
       </c>
       <c r="F24" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G24" t="s">
+        <v>117</v>
+      </c>
+      <c r="H24">
+        <v>80</v>
+      </c>
+      <c r="I24">
+        <v>80</v>
+      </c>
+      <c r="J24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s">
         <v>49</v>
@@ -1652,12 +2126,24 @@
         <v>50</v>
       </c>
       <c r="F25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G25" t="s">
+        <v>118</v>
+      </c>
+      <c r="H25">
+        <v>130</v>
+      </c>
+      <c r="I25">
+        <v>130</v>
+      </c>
+      <c r="J25" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B26" t="s">
         <v>51</v>
@@ -1672,12 +2158,24 @@
         <v>52</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G26" t="s">
+        <v>119</v>
+      </c>
+      <c r="H26">
+        <v>60</v>
+      </c>
+      <c r="I26">
+        <v>60</v>
+      </c>
+      <c r="J26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
         <v>53</v>
@@ -1692,12 +2190,24 @@
         <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G27" t="s">
+        <v>120</v>
+      </c>
+      <c r="H27">
+        <v>60</v>
+      </c>
+      <c r="I27">
+        <v>60</v>
+      </c>
+      <c r="J27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B28" t="s">
         <v>55</v>
@@ -1712,12 +2222,24 @@
         <v>56</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G28" t="s">
+        <v>121</v>
+      </c>
+      <c r="H28">
+        <v>90</v>
+      </c>
+      <c r="I28">
+        <v>90</v>
+      </c>
+      <c r="J28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B29" t="s">
         <v>57</v>
@@ -1732,12 +2254,24 @@
         <v>58</v>
       </c>
       <c r="F29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G29" t="s">
+        <v>122</v>
+      </c>
+      <c r="H29">
+        <v>135</v>
+      </c>
+      <c r="I29">
+        <v>135</v>
+      </c>
+      <c r="J29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s">
         <v>59</v>
@@ -1752,12 +2286,24 @@
         <v>60</v>
       </c>
       <c r="F30" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G30" t="s">
+        <v>123</v>
+      </c>
+      <c r="H30">
+        <v>115</v>
+      </c>
+      <c r="I30">
+        <v>115</v>
+      </c>
+      <c r="J30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s">
         <v>61</v>
@@ -1772,12 +2318,24 @@
         <v>62</v>
       </c>
       <c r="F31" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G31" t="s">
+        <v>124</v>
+      </c>
+      <c r="H31">
+        <v>60</v>
+      </c>
+      <c r="I31">
+        <v>60</v>
+      </c>
+      <c r="J31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s">
         <v>63</v>
@@ -1792,12 +2350,24 @@
         <v>64</v>
       </c>
       <c r="F32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G32" t="s">
+        <v>125</v>
+      </c>
+      <c r="H32">
+        <v>45</v>
+      </c>
+      <c r="I32">
+        <v>45</v>
+      </c>
+      <c r="J32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B33" t="s">
         <v>65</v>
@@ -1812,12 +2382,24 @@
         <v>66</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G33" t="s">
+        <v>126</v>
+      </c>
+      <c r="H33">
+        <v>90</v>
+      </c>
+      <c r="I33">
+        <v>90</v>
+      </c>
+      <c r="J33" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B34" t="s">
         <v>67</v>
@@ -1832,12 +2414,24 @@
         <v>68</v>
       </c>
       <c r="F34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G34" t="s">
+        <v>127</v>
+      </c>
+      <c r="H34">
+        <v>80</v>
+      </c>
+      <c r="I34">
+        <v>80</v>
+      </c>
+      <c r="J34" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B35" t="s">
         <v>69</v>
@@ -1852,12 +2446,24 @@
         <v>70</v>
       </c>
       <c r="F35" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G35" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35">
+        <v>135</v>
+      </c>
+      <c r="I35">
+        <v>135</v>
+      </c>
+      <c r="J35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B36" t="s">
         <v>71</v>
@@ -1872,12 +2478,24 @@
         <v>72</v>
       </c>
       <c r="F36" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G36" t="s">
+        <v>129</v>
+      </c>
+      <c r="H36">
+        <v>45</v>
+      </c>
+      <c r="I36">
+        <v>45</v>
+      </c>
+      <c r="J36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B37" t="s">
         <v>73</v>
@@ -1892,12 +2510,24 @@
         <v>74</v>
       </c>
       <c r="F37" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G37" t="s">
+        <v>130</v>
+      </c>
+      <c r="H37">
+        <v>90</v>
+      </c>
+      <c r="I37">
+        <v>90</v>
+      </c>
+      <c r="J37" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B38" t="s">
         <v>75</v>
@@ -1912,12 +2542,24 @@
         <v>76</v>
       </c>
       <c r="F38" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G38" t="s">
+        <v>131</v>
+      </c>
+      <c r="H38">
+        <v>45</v>
+      </c>
+      <c r="I38">
+        <v>45</v>
+      </c>
+      <c r="J38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B39" t="s">
         <v>77</v>
@@ -1932,52 +2574,153 @@
         <v>78</v>
       </c>
       <c r="F39" t="s">
-        <v>86</v>
+        <v>90</v>
+      </c>
+      <c r="G39" t="s">
+        <v>132</v>
+      </c>
+      <c r="H39">
+        <v>75</v>
+      </c>
+      <c r="I39">
+        <v>75</v>
+      </c>
+      <c r="J39" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:J1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="115" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="110" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="100" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>141</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
